--- a/clean-import-workbooks/Payroll_Workbook_Clean_2026.xlsx
+++ b/clean-import-workbooks/Payroll_Workbook_Clean_2026.xlsx
@@ -5,8 +5,13 @@
   <sheets>
     <sheet name="Biodata" sheetId="1" r:id="rId1"/>
     <sheet name="Pay Sheet" sheetId="2" r:id="rId2"/>
-    <sheet name="Terminations" sheetId="3" r:id="rId3"/>
-    <sheet name="Reengagement Wages" sheetId="4" r:id="rId4"/>
+    <sheet name="Final" sheetId="3" r:id="rId3"/>
+    <sheet name="Wages" sheetId="4" r:id="rId4"/>
+    <sheet name="Combined Pay" sheetId="5" r:id="rId5"/>
+    <sheet name="Res-Workers" sheetId="6" r:id="rId6"/>
+    <sheet name="Shop-Workers" sheetId="7" r:id="rId7"/>
+    <sheet name="Terminations" sheetId="8" r:id="rId8"/>
+    <sheet name="Reengagement Wages" sheetId="9" r:id="rId9"/>
   </sheets>
 </workbook>
 </file>
@@ -1930,14 +1935,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:Q34"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Employee No</v>
       </c>
       <c r="B1" t="str">
-        <v>Name of Employee</v>
+        <v>Full Name</v>
       </c>
       <c r="C1" t="str">
         <v>Basic Salary</v>
@@ -1964,30 +1969,42 @@
         <v>Days Worked</v>
       </c>
       <c r="K1" t="str">
+        <v>Days Absent</v>
+      </c>
+      <c r="L1" t="str">
         <v>Overtime Hours</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
+        <v>Overtime Amount</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Bonus Amount</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Gift Amount</v>
+      </c>
+      <c r="P1" t="str">
+        <v>Leave Pay Amount</v>
+      </c>
+      <c r="Q1" t="str">
         <v>Notes</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>CITI10</v>
-      </c>
       <c r="B2" t="str">
-        <v>Simikizani Siki</v>
+        <v>Count</v>
       </c>
       <c r="C2">
-        <v>70000</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>70000</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>70000</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1998,28 +2015,22 @@
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="L2" t="str">
-        <v>Imported from card layout block row 44</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>CITI14</v>
-      </c>
       <c r="B3" t="str">
-        <v>Madalitso Baluti</v>
+        <v>Martin Kandalama</v>
       </c>
       <c r="C3">
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -2030,28 +2041,22 @@
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="L3" t="str">
-        <v>Imported from card layout block row 59</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>CITI18</v>
-      </c>
       <c r="B4" t="str">
-        <v>Esnat Adam</v>
+        <v>Daniel Mponda</v>
       </c>
       <c r="C4">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -2062,28 +2067,22 @@
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="L4" t="str">
-        <v>Imported from card layout block row 74</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>CITI19</v>
-      </c>
       <c r="B5" t="str">
-        <v>Martin Kandalama</v>
+        <v>Elizabeth Kabudula</v>
       </c>
       <c r="C5">
-        <v>70000</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>70000</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>70000</v>
+        <v>0</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -2094,28 +2093,22 @@
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="L5" t="str">
-        <v>Imported from card layout block row 9</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>CITI23</v>
-      </c>
       <c r="B6" t="str">
         <v>William Mahinya</v>
       </c>
       <c r="C6">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -2126,22 +2119,16 @@
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="L6" t="str">
-        <v>Imported from card layout block row 24</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>CITI27</v>
-      </c>
       <c r="B7" t="str">
         <v>Yankho Gulani</v>
       </c>
       <c r="C7">
-        <v>120000</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>120000</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -2158,82 +2145,7046 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="L7" t="str">
-        <v>Imported from card layout block row 39</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v>CITI18</v>
-      </c>
       <c r="B8" t="str">
+        <v>Sapulene Mkulichi</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="str">
+        <v>George Matemba</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="str">
+        <v>Alinafe James</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="str">
+        <v>Chimwemwe Banda</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="str">
+        <v>Maureen Ulaya</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="str">
+        <v>Francis Chatsweka</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="str">
+        <v>Stenala Mponda</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="str">
+        <v>Simikizani Siki</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="str">
+        <v>Amini Wecha</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="str">
+        <v>Tayifolo Mandowa</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="str">
+        <v>Monica George</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="str">
+        <v>Madalitso Baluti</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="str">
+        <v>Peter James</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="str">
+        <v>Maggie Billy</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="str">
         <v>Esnat Adam</v>
       </c>
-      <c r="C8">
-        <v>80000</v>
-      </c>
-      <c r="D8">
-        <v>80000</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="L8" t="str">
-        <v>Imported from card layout block row 69</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>CITI30</v>
-      </c>
-      <c r="B9" t="str">
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="str">
+        <v>Agness  Mponda</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="str">
+        <v>Elizabeth Chinkono</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="str">
         <v>Dancan Botha</v>
       </c>
-      <c r="C9">
-        <v>94000</v>
-      </c>
-      <c r="D9">
-        <v>94000</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="L9" t="str">
-        <v>Imported from card layout block row 85</v>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="str">
+        <v>Ibrahim Amadu</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="str">
+        <v>Amounts Due</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="str">
+        <v>Management Employees</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="str">
+        <v>Domasi Supermarket Employees</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="str">
+        <v>Stop-Over Employees</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="str">
+        <v>Restuarant Employees</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="str">
+        <v>Domasi Residence Employees</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="str">
+        <v>Nyambadwe Residence Employees</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="str">
+        <v>Chinyonga Supermarket Employees</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q34"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Q33"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Employee No</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Full Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Basic Salary</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Gross Pay</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Total Deductions</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Net Pay</v>
+      </c>
+      <c r="G1" t="str">
+        <v>PAYE</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Loan Deduction</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Other Deductions</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Days Worked</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Days Absent</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Overtime Hours</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Overtime Amount</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Bonus Amount</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Gift Amount</v>
+      </c>
+      <c r="P1" t="str">
+        <v>Leave Pay Amount</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>Notes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="str">
+        <v>Count</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="str">
+        <v>Martin Kandalama</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="str">
+        <v>Daniel Mponda</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="str">
+        <v>Elizabeth Kabudula</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="str">
+        <v>Yankho Gulani</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="str">
+        <v>William Mahinya</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="str">
+        <v>George Matemba</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="str">
+        <v>Alinafe James</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="str">
+        <v>Chimwemwe Banda</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="str">
+        <v>Maureen Ulaya</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="str">
+        <v>Francis Chatsweka</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="str">
+        <v>Stenala Mponda</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="str">
+        <v>Simikizani Siki</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="str">
+        <v>Amini Wecha</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="str">
+        <v>Tayifolo Mandowa</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="str">
+        <v>Monica George</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="str">
+        <v>Madalitso Baluti</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="str">
+        <v>Peter James</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="str">
+        <v>Maggie Billy</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="str">
+        <v>Esnat Adam</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="str">
+        <v>Agness  Mponda</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="str">
+        <v>Elizabeth Chinkono</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="str">
+        <v>Dancan Botha</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="str">
+        <v>Ibrahim Amadu</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="str">
+        <v>Amounts Due</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="str">
+        <v>Management Employees</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="str">
+        <v>Domasi Supermarket Employees</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="str">
+        <v>Stop-Over Employees</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="str">
+        <v>Restuarant Employees</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="str">
+        <v>Domasi Residence Employees</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="str">
+        <v>Nyambadwe Residence Employees</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="str">
+        <v>Chinyonga Supermarket Employees</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q33"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Q95"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Employee No</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Full Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Basic Salary</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Gross Pay</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Total Deductions</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Net Pay</v>
+      </c>
+      <c r="G1" t="str">
+        <v>PAYE</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Loan Deduction</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Other Deductions</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Days Worked</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Days Absent</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Overtime Hours</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Overtime Amount</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Bonus Amount</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Gift Amount</v>
+      </c>
+      <c r="P1" t="str">
+        <v>Leave Pay Amount</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>Notes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="str">
+        <v>First</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="str">
+        <v>Month to pay</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="str">
+        <v>Next</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="str">
+        <v>Position in month</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="str">
+        <v>Mid</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="str">
+        <v>January 2026</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="str">
+        <v>&lt;---- position in month</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="str">
+        <v>Citi-Nati Shopping Centre</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="str">
+        <v>Name of Employee</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="str">
+        <v>Employee Number</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="str">
+        <v>Gross Salary</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="str">
+        <v>Overtime Claim</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="str">
+        <v>P.A.Y.E</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="str">
+        <v>Xmas Gift/Leave Pay</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="str">
+        <v>Medical Aid Scheme</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="str">
+        <v>Loan Instalment</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="str">
+        <v>Absence Deduction</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="str">
+        <v>Loan Balance</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="str">
+        <v>Net Pay for the Month</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="str">
+        <v>Net Pay mid and end of Month</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="str">
+        <v>Payslip for the Month</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="str">
+        <v>Note: Repayment date of any loan should not go beyond December of current year</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="str">
+        <v>OVERTIME DAYS</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="str">
+        <v>Emp No</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="str">
+        <v>CITI01</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="str">
+        <v>CITI02</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="str">
+        <v>CITI04</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="str">
+        <v>CITI05</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="str">
+        <v>CITI06</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="str">
+        <v>CITI07</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="str">
+        <v>CITI08</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="str">
+        <v>CITI09</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="str">
+        <v>CITI10</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="str">
+        <v>CITI11</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="str">
+        <v>CITI12</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="str">
+        <v>CITI13</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="str">
+        <v>CITI14</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="str">
+        <v>CITI15</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="str">
+        <v>CITI16</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="str">
+        <v>CITI17</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="str">
+        <v>CITI18</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="str">
+        <v>CITI19</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="str">
+        <v>CITI20</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="str">
+        <v>CITI21</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="str">
+        <v>CITI22</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="str">
+        <v>CITI23</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="str">
+        <v>CITI24</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="str">
+        <v>CITI25</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="str">
+        <v>CITI26</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="str">
+        <v>CITI27</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="str">
+        <v>CITI28</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="str">
+        <v>CITI29</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="str">
+        <v>CITI30</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="str">
+        <v>CITI31</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="str">
+        <v>Net wages to pay Full Month</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="str">
+        <v>Net wages to pay Twice a Month</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="str">
+        <v>The forms below should only be used when contract expires, or an employee resigns or is dismissed</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="str">
+        <v>Date of Termination</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="str">
+        <v>Date Contract Terminated</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="str">
+        <v>Employee Received Half Pay Wage?</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="str">
+        <v>Payslip for end of Contract</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="str">
+        <v>Number of Months Worked Continously</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="str">
+        <v>Deductions made during the Month</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="str">
+        <v>Gratuity at 5% of the last salary mutiplied by Number of Months of Uninterrupted Employment</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="str">
+        <v>Amount Paid in Month of Termination</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="str">
+        <v>Leave Pay on Accrued Leave Days</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="str">
+        <v>Madalitso Baluti</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="str">
+        <v>Peter James</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="str">
+        <v>Less Outstanding Loan Obligations</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="str">
+        <v>Less part-payment of Salary made during mid month of</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="str">
+        <v>Daniel Mponda</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="str">
+        <v>William Mahinya</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="str">
+        <v>Employee's Signature agreeing to the amount due following end of Contract</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="str">
+        <v>Date signed</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="str">
+        <v>Yankho Gulani</v>
+      </c>
+      <c r="C77">
+        <v>0</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="str">
+        <v>Agness  Mponda</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
+      <c r="D78">
+        <v>0</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="str">
+        <v>Elizabeth Chinkono</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+      <c r="D79">
+        <v>0</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="str">
+        <v>Employee Resignation/Dismissal</v>
+      </c>
+      <c r="C80">
+        <v>0</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="str">
+        <v>Ibrahim Amadu</v>
+      </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
+      <c r="D81">
+        <v>0</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="str">
+        <v>Domasi Supermarket</v>
+      </c>
+      <c r="C82">
+        <v>0</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="str">
+        <v>Restaurant</v>
+      </c>
+      <c r="C83">
+        <v>0</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="str">
+        <v>Nyambadwe</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="str">
+        <v>Number of days worked during month of resignation/dismissal</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="str">
+        <v>Salary for days worked during month of resignation/dismissal</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="str">
+        <v>One Month Pay In Lieu of Notice</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+      <c r="D87">
+        <v>0</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="str">
+        <v>Difference</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="str">
+        <v>Employer's Signature Confirming Payment of the Net Amount Due Following End of Contract</v>
+      </c>
+      <c r="C89">
+        <v>0</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>CITI01</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Sapulene Mkulichi</v>
+      </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="str">
+        <v>Imported from card layout block row 14</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>CITI10</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Simikizani Siki</v>
+      </c>
+      <c r="C91">
+        <v>70000</v>
+      </c>
+      <c r="D91">
+        <v>70000</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91">
+        <v>70000</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="str">
+        <v>Imported from card layout block row 44</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>CITI14</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Madalitso Baluti</v>
+      </c>
+      <c r="C92">
+        <v>90000</v>
+      </c>
+      <c r="D92">
+        <v>90000</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92">
+        <v>90000</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="str">
+        <v>Imported from card layout block row 59</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>CITI18</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Esnat Adam</v>
+      </c>
+      <c r="C93">
+        <v>80000</v>
+      </c>
+      <c r="D93">
+        <v>80000</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93">
+        <v>80000</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="str">
+        <v>Imported from card layout block row 74</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Gross Salary</v>
+      </c>
+      <c r="C94">
+        <v>0</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="str">
+        <v>Imported from card layout block row 179</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="str">
+        <v>Employee does not exist</v>
+      </c>
+      <c r="C95">
+        <v>0</v>
+      </c>
+      <c r="D95">
+        <v>0</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="str">
+        <v>Imported from card layout block row 218</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q95"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Q27"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Employee No</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Full Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Basic Salary</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Gross Pay</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Total Deductions</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Net Pay</v>
+      </c>
+      <c r="G1" t="str">
+        <v>PAYE</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Loan Deduction</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Other Deductions</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Days Worked</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Days Absent</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Overtime Hours</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Overtime Amount</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Bonus Amount</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Gift Amount</v>
+      </c>
+      <c r="P1" t="str">
+        <v>Leave Pay Amount</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>Notes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="str">
+        <v>Amount Due</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="str">
+        <v>Count</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="str">
+        <v>Martin Kandalama</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="str">
+        <v>Daniel Mponda</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="str">
+        <v>Elizabeth Kabudula</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="str">
+        <v>William Mahinya</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="str">
+        <v>Yankho Gulani</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="str">
+        <v>Sapulene Mkulichi</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="str">
+        <v>George Matemba</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="str">
+        <v>Alinafe James</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="str">
+        <v>Chimwemwe Banda</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="str">
+        <v>Maureen Ulaya</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="str">
+        <v>Francis Chatsweka</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="str">
+        <v>Stenala Mponda</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="str">
+        <v>Simikizani Siki</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="str">
+        <v>Amini Wecha</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="str">
+        <v>Tayifolo Mandowa</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="str">
+        <v>Monica George</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="str">
+        <v>Madalitso Baluti</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="str">
+        <v>Peter James</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="str">
+        <v>Maggie Billy</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="str">
+        <v>Esnat Adam</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="str">
+        <v>Agness  Mponda</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="str">
+        <v>Elizabeth Chinkono</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="str">
+        <v>Dancan Botha</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="str">
+        <v>Ibrahim Amadu</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q27"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Q32"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Employee No</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Full Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Basic Salary</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Gross Pay</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Total Deductions</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Net Pay</v>
+      </c>
+      <c r="G1" t="str">
+        <v>PAYE</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Loan Deduction</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Other Deductions</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Days Worked</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Days Absent</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Overtime Hours</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Overtime Amount</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Bonus Amount</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Gift Amount</v>
+      </c>
+      <c r="P1" t="str">
+        <v>Leave Pay Amount</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>Notes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="str">
+        <v>Gross Wages</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="str">
+        <v>P.A.Y.E</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="str">
+        <v>Christimas Gift/Leave Pay</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="str">
+        <v>Citi-Nati Shopping Centre</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="str">
+        <v>Name of Employee</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="str">
+        <v>Employee Number</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="str">
+        <v>January 2026</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="str">
+        <v>Gross Salary</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="str">
+        <v>Overtime Claim</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="str">
+        <v>Xmas Gift/Leave Pay</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="str">
+        <v>Medical Aid Scheme</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="str">
+        <v>Loan Instalment</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="str">
+        <v>Absence Deduction</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="str">
+        <v>Loan Balance</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="str">
+        <v>Net Pay for the Month</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="str">
+        <v>Net Pay mid and end of Month</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="str">
+        <v>Payslip for the Month</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="str">
+        <v>List of Employees and their dues</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="str">
+        <v>Eployee Number</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="str">
+        <v>CITI19</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="str">
+        <v>CITI20</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="str">
+        <v>CITI21</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="str">
+        <v>CITI22</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="str">
+        <v>CITI23</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="str">
+        <v>CITI24</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="str">
+        <v>CITI25</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="str">
+        <v>CITI26</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="str">
+        <v>CITI27</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>CITI19</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Martin Kandalama</v>
+      </c>
+      <c r="C30">
+        <v>70000</v>
+      </c>
+      <c r="D30">
+        <v>70000</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>70000</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="str">
+        <v>Imported from card layout block row 9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>CITI23</v>
+      </c>
+      <c r="B31" t="str">
+        <v>William Mahinya</v>
+      </c>
+      <c r="C31">
+        <v>150000</v>
+      </c>
+      <c r="D31">
+        <v>150000</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>150000</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="str">
+        <v>Imported from card layout block row 24</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>CITI27</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Yankho Gulani</v>
+      </c>
+      <c r="C32">
+        <v>120000</v>
+      </c>
+      <c r="D32">
+        <v>120000</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="str">
+        <v>Imported from card layout block row 39</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q32"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Q46"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Employee No</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Full Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Basic Salary</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Gross Pay</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Total Deductions</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Net Pay</v>
+      </c>
+      <c r="G1" t="str">
+        <v>PAYE</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Loan Deduction</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Other Deductions</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Days Worked</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Days Absent</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Overtime Hours</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Overtime Amount</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Bonus Amount</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Gift Amount</v>
+      </c>
+      <c r="P1" t="str">
+        <v>Leave Pay Amount</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>Notes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="str">
+        <v>Gross Wages</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="str">
+        <v>P.A.Y.E</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="str">
+        <v>Christmas Gift/Leave Pay</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="str">
+        <v>Citi-Nati Shopping Centre</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="str">
+        <v>Name of Employee</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="str">
+        <v>Employee Number</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="str">
+        <v>Payslip for the Month</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="str">
+        <v>Gross Salary</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="str">
+        <v>Overtime Claim</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="str">
+        <v>Xmas Gift/Leave Pay</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="str">
+        <v>Medical Aid Scheme</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="str">
+        <v>Loan Instalment</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="str">
+        <v>Absence Deduction</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="str">
+        <v>Loan Balance</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="str">
+        <v>Net Pay for the Month</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="str">
+        <v>Net Pay mid and end of Month</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="str">
+        <v>List of Employees and their dues</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="str">
+        <v>Eployee Number</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="str">
+        <v>CITI01</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="str">
+        <v>CITI02</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="str">
+        <v>CITI03</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="str">
+        <v>CITI04</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="str">
+        <v>CITI05</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="str">
+        <v>CITI06</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="str">
+        <v>CITI07</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="str">
+        <v>CITI08</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="str">
+        <v>CITI09</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="str">
+        <v>CITI10</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="str">
+        <v>CITI11</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="str">
+        <v>CITI12</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="str">
+        <v>CITI13</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="str">
+        <v>CITI14</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="str">
+        <v>CITI15</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="str">
+        <v>CITI16</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="str">
+        <v>CITI17</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="str">
+        <v>CITI18</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="str">
+        <v>CITI28</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="str">
+        <v>CITI29</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="str">
+        <v>CITI30</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="str">
+        <v>CITI31</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>CITI01</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Sapulene Mkulichi</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="str">
+        <v>Imported from card layout block row 9</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>CITI10</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Simikizani Siki</v>
+      </c>
+      <c r="C43">
+        <v>70000</v>
+      </c>
+      <c r="D43">
+        <v>70000</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>70000</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="str">
+        <v>Imported from card layout block row 39</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>CITI14</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Madalitso Baluti</v>
+      </c>
+      <c r="C44">
+        <v>90000</v>
+      </c>
+      <c r="D44">
+        <v>90000</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>90000</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="str">
+        <v>Imported from card layout block row 54</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>CITI18</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Esnat Adam</v>
+      </c>
+      <c r="C45">
+        <v>80000</v>
+      </c>
+      <c r="D45">
+        <v>80000</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="str">
+        <v>Imported from card layout block row 69</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>CITI30</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Dancan Botha</v>
+      </c>
+      <c r="C46">
+        <v>94000</v>
+      </c>
+      <c r="D46">
+        <v>94000</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="str">
+        <v>Imported from card layout block row 85</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q46"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H4"/>
   <sheetData>
@@ -2303,7 +9254,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H25"/>
   <sheetData>
